--- a/public/Analyses_covered/Analyses_viewed_in_class.xlsx
+++ b/public/Analyses_covered/Analyses_viewed_in_class.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nmyszkowski/Documents/GitHub/personal-website-2022/static/Analyses_covered/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F6C530-6E83-B649-B75D-1C009FCC63C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428953EA-234E-B74C-AB8D-3631CC09C687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="140" yWindow="1040" windowWidth="25040" windowHeight="21280" xr2:uid="{3C13C7B6-1A00-7E46-92D7-E11AFB1CA539}"/>
   </bookViews>
@@ -331,9 +331,6 @@
     <t>https://youtu.be/u4DFSP7i38U</t>
   </si>
   <si>
-    <t>https://youtu.be/f3W7DpnkAAw</t>
-  </si>
-  <si>
     <t>https://youtu.be/Fpjtg9aGNzQ</t>
   </si>
   <si>
@@ -400,9 +397,6 @@
     <t>https://youtu.be/S1KxDNqmbic</t>
   </si>
   <si>
-    <t>https://youtu.be/dCI_H1XBc0w</t>
-  </si>
-  <si>
     <t>https://youtu.be/LV5mCV2ycwY</t>
   </si>
   <si>
@@ -503,6 +497,12 @@
   </si>
   <si>
     <t>https://youtu.be/DuC7cEgM188</t>
+  </si>
+  <si>
+    <t>https://youtu.be/i___hfa_Wjs</t>
+  </si>
+  <si>
+    <t>https://youtu.be/iAdDbU694Ao</t>
   </si>
 </sst>
 </file>
@@ -900,7 +900,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B1" t="s">
         <v>6</v>
@@ -915,13 +915,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I1" t="s">
         <v>5</v>
@@ -936,7 +936,7 @@
         <v>2</v>
       </c>
       <c r="M1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -953,10 +953,10 @@
         <v>50</v>
       </c>
       <c r="J2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -1029,10 +1029,10 @@
         <v>34</v>
       </c>
       <c r="J7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -1049,30 +1049,30 @@
         <v>34</v>
       </c>
       <c r="J8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" t="s">
         <v>110</v>
-      </c>
-      <c r="B9" t="s">
-        <v>111</v>
       </c>
       <c r="C9" t="s">
         <v>44</v>
       </c>
       <c r="L9" t="s">
+        <v>111</v>
+      </c>
+      <c r="M9" t="s">
         <v>112</v>
-      </c>
-      <c r="M9" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
@@ -1097,10 +1097,10 @@
         <v>44</v>
       </c>
       <c r="L11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
@@ -1170,7 +1170,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
@@ -1182,12 +1182,12 @@
         <v>35</v>
       </c>
       <c r="J16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s">
         <v>16</v>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B20" t="s">
         <v>60</v>
@@ -1247,12 +1247,12 @@
         <v>96</v>
       </c>
       <c r="L20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B21" t="s">
         <v>59</v>
@@ -1264,7 +1264,7 @@
         <v>35</v>
       </c>
       <c r="J21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
@@ -1298,12 +1298,12 @@
         <v>35</v>
       </c>
       <c r="J23" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B24" t="s">
         <v>56</v>
@@ -1315,7 +1315,7 @@
         <v>35</v>
       </c>
       <c r="J24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
@@ -1332,7 +1332,7 @@
         <v>35</v>
       </c>
       <c r="J25" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
@@ -1380,7 +1380,7 @@
         <v>35</v>
       </c>
       <c r="J28" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
@@ -1417,7 +1417,7 @@
         <v>91</v>
       </c>
       <c r="J30" t="s">
-        <v>98</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
@@ -1434,13 +1434,13 @@
         <v>91</v>
       </c>
       <c r="J31" t="s">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="K31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
@@ -1457,7 +1457,7 @@
         <v>13</v>
       </c>
       <c r="J32" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
@@ -1465,7 +1465,7 @@
         <v>71</v>
       </c>
       <c r="B33" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E33" t="s">
         <v>14</v>
@@ -1474,7 +1474,7 @@
         <v>35</v>
       </c>
       <c r="J33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
@@ -1494,7 +1494,7 @@
         <v>74</v>
       </c>
       <c r="L34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
@@ -1514,7 +1514,7 @@
         <v>74</v>
       </c>
       <c r="K35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
@@ -1533,10 +1533,10 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B37" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F37" t="s">
         <v>50</v>
@@ -1545,15 +1545,15 @@
         <v>13</v>
       </c>
       <c r="J37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B38" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F38" t="s">
         <v>50</v>
@@ -1562,12 +1562,12 @@
         <v>13</v>
       </c>
       <c r="J38" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B39" t="s">
         <v>78</v>
@@ -1579,15 +1579,15 @@
         <v>13</v>
       </c>
       <c r="J39" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B40" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F40" t="s">
         <v>50</v>
@@ -1596,7 +1596,7 @@
         <v>13</v>
       </c>
       <c r="M40" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
@@ -1604,7 +1604,7 @@
         <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F41" t="s">
         <v>50</v>
@@ -1613,7 +1613,7 @@
         <v>13</v>
       </c>
       <c r="J41" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
@@ -1638,7 +1638,7 @@
         <v>50</v>
       </c>
       <c r="J43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
@@ -1671,27 +1671,27 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B46" t="s">
+        <v>126</v>
+      </c>
+      <c r="J46" t="s">
         <v>128</v>
-      </c>
-      <c r="J46" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B47" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C47" t="s">
         <v>44</v>
       </c>
       <c r="M47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
